--- a/Modelo Pessoas/Modelo 1.xlsx
+++ b/Modelo Pessoas/Modelo 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joh_gomes\Desktop\Magalog CDs\Modelo Pessoas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BF47DB9-CF13-4AC3-B775-98B547F4E899}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43C3C3-FC6C-4D78-8EFE-EFB29F5645EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15960" xr2:uid="{3DEAAAD0-9C2B-4DB4-888D-528E2D2BC099}"/>
+    <workbookView xWindow="4125" yWindow="960" windowWidth="28800" windowHeight="14280" xr2:uid="{3DEAAAD0-9C2B-4DB4-888D-528E2D2BC099}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha3" sheetId="3" r:id="rId1"/>
@@ -19552,7 +19552,6 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AI188" xr:uid="{E07045E1-939D-4777-AF82-73FD4A3726D6}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
--- a/Modelo Pessoas/Modelo 1.xlsx
+++ b/Modelo Pessoas/Modelo 1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joh_gomes\Desktop\Magalog CDs\Modelo Pessoas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E43C3C3-FC6C-4D78-8EFE-EFB29F5645EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BFBB26-7C71-4CFA-9985-AF751A6A9988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4125" yWindow="960" windowWidth="28800" windowHeight="14280" xr2:uid="{3DEAAAD0-9C2B-4DB4-888D-528E2D2BC099}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15960" xr2:uid="{3DEAAAD0-9C2B-4DB4-888D-528E2D2BC099}"/>
   </bookViews>
   <sheets>
     <sheet name="Planilha3" sheetId="3" r:id="rId1"/>
@@ -3353,7 +3353,7 @@
         <v>31645</v>
       </c>
       <c r="L6" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="S6" t="s">
         <v>793</v>
@@ -3392,7 +3392,7 @@
         <v>169959</v>
       </c>
       <c r="AF6" t="s">
-        <v>265</v>
+        <v>245</v>
       </c>
       <c r="AG6">
         <v>6</v>

--- a/Modelo Pessoas/Modelo 1.xlsx
+++ b/Modelo Pessoas/Modelo 1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\joh_gomes\Desktop\Magalog CDs\Modelo Pessoas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80BFBB26-7C71-4CFA-9985-AF751A6A9988}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E411736-58E3-40F2-8F4D-A3A08E3A9A80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="15960" xr2:uid="{3DEAAAD0-9C2B-4DB4-888D-528E2D2BC099}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2582" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2583" uniqueCount="800">
   <si>
     <t>ID</t>
   </si>
@@ -3355,6 +3355,12 @@
       <c r="L6" t="s">
         <v>245</v>
       </c>
+      <c r="P6">
+        <v>255690</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>304</v>
+      </c>
       <c r="S6" t="s">
         <v>793</v>
       </c>
